--- a/data/processed/positivacao/2022-01_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-01_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24737,7 +24737,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B939" t="inlineStr"/>
@@ -36245,7 +36245,7 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr"/>
@@ -65033,7 +65033,7 @@
     <row r="2490">
       <c r="A2490" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2490" t="inlineStr"/>
@@ -66704,12 +66704,12 @@
       <c r="A2555" t="inlineStr"/>
       <c r="B2555" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 91 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 73 cliente(s), não positivou 765 cliente(s) - Total vendido: R$ 71.025,80
-Vendedor 3 - FERNANDA: positivou 99 cliente(s), não positivou 343 cliente(s) - Total vendido: R$ 113.350,68
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 99 cliente(s), não positivou 343 cliente(s) - Total vendido: R$ 113.350,68
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 8 cliente(s), não positivou 449 cliente(s) - Total vendido: R$ 1.107,25
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2555" t="inlineStr"/>
